--- a/docs/onboarding/Users_template.xlsx
+++ b/docs/onboarding/Users_template.xlsx
@@ -418,10 +418,10 @@
         <v>apellido</v>
       </c>
       <c r="D1" t="str">
-        <v>rol (opcional)</v>
+        <v>rol</v>
       </c>
       <c r="E1" t="str">
-        <v>clases (opcional)</v>
+        <v>clases</v>
       </c>
     </row>
   </sheetData>

--- a/docs/onboarding/Users_template.xlsx
+++ b/docs/onboarding/Users_template.xlsx
@@ -4,7 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
-    <sheet name="Clases" sheetId="2" r:id="rId2"/>
+    <sheet name="Asignaturas" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -421,7 +421,7 @@
         <v>rol</v>
       </c>
       <c r="E1" t="str">
-        <v>clases</v>
+        <v>asignaturas</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
         <v>nombre</v>
       </c>
       <c r="B1" t="str">
-        <v>fechaInicio (opcional)</v>
+        <v>precio</v>
       </c>
       <c r="C1" t="str">
-        <v>precio (opcional)</v>
+        <v>tipoPrecio</v>
       </c>
       <c r="D1" t="str">
-        <v>tipoPrecio (opcional)</v>
+        <v>fechaInicio</v>
       </c>
       <c r="E1" t="str">
         <v>profesorEmail (opcional)</v>

--- a/docs/onboarding/Users_template.xlsx
+++ b/docs/onboarding/Users_template.xlsx
@@ -455,7 +455,7 @@
         <v>precio</v>
       </c>
       <c r="C1" t="str">
-        <v>tipoPrecio</v>
+        <v>cuotas (opcional)</v>
       </c>
       <c r="D1" t="str">
         <v>fechaInicio</v>
